--- a/xls/square_12_tri3_21.xlsx
+++ b/xls/square_12_tri3_21.xlsx
@@ -482,13 +482,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>-0.31710712235409805</v>
+        <v>-0.31710712655950607</v>
       </c>
       <c r="J21">
-        <v>-0.3068673078982203</v>
+        <v>-0.3068673116855741</v>
       </c>
       <c r="K21">
-        <v>3.9502550783815686</v>
+        <v>3.950255082182251</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -517,13 +517,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-0.00015598057283512542</v>
+        <v>-0.00015598057265892775</v>
       </c>
       <c r="J22">
-        <v>-0.00012741352367362784</v>
+        <v>-0.00012741352357933716</v>
       </c>
       <c r="K22">
-        <v>2.435731100383792</v>
+        <v>2.4357311006107705</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -552,13 +552,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-0.0011781299747634709</v>
+        <v>-0.0011781299763548238</v>
       </c>
       <c r="J23">
-        <v>-0.0008058967889329763</v>
+        <v>-0.0008058967899790895</v>
       </c>
       <c r="K23">
-        <v>2.7274206691159018</v>
+        <v>2.7274206697917167</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -587,13 +587,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-8.518247901962628e-5</v>
+        <v>-8.51824789942595e-5</v>
       </c>
       <c r="J24">
-        <v>-6.370826083989522e-5</v>
+        <v>-6.370826082542818e-5</v>
       </c>
       <c r="K24">
-        <v>2.2480055503820955</v>
+        <v>2.248005550134853</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -622,13 +622,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-0.00021419823403817816</v>
+        <v>-0.00021419823401449224</v>
       </c>
       <c r="J25">
-        <v>-0.00014811468100344482</v>
+        <v>-0.00014811468098940907</v>
       </c>
       <c r="K25">
-        <v>2.3781414435393198</v>
+        <v>2.3781414433950996</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -657,13 +657,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-0.0001271025717083313</v>
+        <v>-0.00012710257171040518</v>
       </c>
       <c r="J26">
-        <v>-9.091603687960902e-5</v>
+        <v>-9.09160368813934e-5</v>
       </c>
       <c r="K26">
-        <v>2.299553902690925</v>
+        <v>2.299553902737185</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -692,13 +692,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-0.00012293776962046902</v>
+        <v>-0.00012293776961328274</v>
       </c>
       <c r="J27">
-        <v>-9.136752992924753e-5</v>
+        <v>-9.136752992481069e-5</v>
       </c>
       <c r="K27">
-        <v>2.3200278254262665</v>
+        <v>2.3200278256004383</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -727,13 +727,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-9.647734692677929e-5</v>
+        <v>-9.64773469403311e-5</v>
       </c>
       <c r="J28">
-        <v>-6.776333052919659e-5</v>
+        <v>-6.7763330537684e-5</v>
       </c>
       <c r="K28">
-        <v>2.225345671901039</v>
+        <v>2.2253456719672218</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -762,13 +762,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-6.368352333093919e-5</v>
+        <v>-6.368352332968538e-5</v>
       </c>
       <c r="J29">
-        <v>-4.8175662536836786e-5</v>
+        <v>-4.81756625362099e-5</v>
       </c>
       <c r="K29">
-        <v>2.190898386256731</v>
+        <v>2.1908983862946436</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -797,13 +797,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-0.00011479774551012436</v>
+        <v>-0.00011479774549517333</v>
       </c>
       <c r="J30">
-        <v>-7.826718519535731e-5</v>
+        <v>-7.826718518523005e-5</v>
       </c>
       <c r="K30">
-        <v>2.24114184642921</v>
+        <v>2.2411418464471726</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -832,13 +832,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-9.03597387727714e-6</v>
+        <v>-9.03597387968801e-6</v>
       </c>
       <c r="J31">
-        <v>-1.581699313893793e-5</v>
+        <v>-1.5816993140143382e-5</v>
       </c>
       <c r="K31">
-        <v>2.1424746125296257</v>
+        <v>2.142474612677549</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -867,13 +867,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>6.174817559982391e-6</v>
+        <v>6.17481756056098e-6</v>
       </c>
       <c r="J32">
         <v>-5.02624775035403e-7</v>
       </c>
       <c r="K32">
-        <v>1.9056773219658798</v>
+        <v>1.9056773217628544</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_12_tri3_21.xlsx
+++ b/xls/square_12_tri3_21.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>484</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>169</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>400</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19">
+        <v>2166</v>
+      </c>
+      <c r="I19">
+        <v>1.4328112553072474</v>
+      </c>
+      <c r="J19">
+        <v>-1.2593243900476905</v>
+      </c>
+      <c r="K19">
+        <v>3.0122992206199015</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20">
+        <v>484</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>169</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>441</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>2400</v>
+      </c>
+      <c r="I20">
+        <v>-0.6287314136456975</v>
+      </c>
+      <c r="J20">
+        <v>-0.5765859731048094</v>
+      </c>
+      <c r="K20">
+        <v>3.8236275216772424</v>
+      </c>
+    </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
         <v>11</v>
